--- a/data/stats/supp_tables/fallcover-soilcover-cctill-estimates.xlsx
+++ b/data/stats/supp_tables/fallcover-soilcover-cctill-estimates.xlsx
@@ -11,6 +11,59 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="16">
+  <si>
+    <t>cctrt_id</t>
+  </si>
+  <si>
+    <t>till_id</t>
+  </si>
+  <si>
+    <t>response</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>asymp.LCL</t>
+  </si>
+  <si>
+    <t>asymp.UCL</t>
+  </si>
+  <si>
+    <t>mix_E</t>
+  </si>
+  <si>
+    <t>inversion</t>
+  </si>
+  <si>
+    <t>Inf</t>
+  </si>
+  <si>
+    <t>mix_M</t>
+  </si>
+  <si>
+    <t>nocc</t>
+  </si>
+  <si>
+    <t>rad_L</t>
+  </si>
+  <si>
+    <t>rad_M</t>
+  </si>
+  <si>
+    <t>notill</t>
+  </si>
+  <si>
+    <t>surface</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,476 +407,372 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>cctrt_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>till_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>response</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>df</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>asymp.LCL</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>asymp.UCL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mix_E</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>inversion</t>
-        </is>
+    <row r="1" spans="1:7" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>0.865477287448907</v>
+        <v>0.8654774397956561</v>
       </c>
       <c r="D2">
-        <v>0.01534459285783242</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.0153446449672952</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0.8324695568382263</v>
+        <v>0.8324695825305269</v>
       </c>
       <c r="G2">
-        <v>0.89281897274138</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mix_M</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>inversion</t>
-        </is>
+        <v>0.8928192055464582</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>0.7311613850887738</v>
+        <v>0.7311629605022052</v>
       </c>
       <c r="D3">
-        <v>0.02416182360996421</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.02416187350935078</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>0.6812675184585001</v>
+        <v>0.6812689569131966</v>
       </c>
       <c r="G3">
-        <v>0.775815086141177</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>nocc</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>inversion</t>
-        </is>
+        <v>0.7758167219154196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>0.6994663811195707</v>
+        <v>0.69946691303645</v>
       </c>
       <c r="D4">
-        <v>0.02580736104233486</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.02580748052554061</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>0.6466024608063166</v>
+        <v>0.6466027289486839</v>
       </c>
       <c r="G4">
-        <v>0.7475103966090726</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>rad_L</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>inversion</t>
-        </is>
+        <v>0.7475111302901476</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>0.6707028090168078</v>
+        <v>0.6707035952549945</v>
       </c>
       <c r="D5">
-        <v>0.02689109091788674</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.02689120915647518</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>0.6160292701306981</v>
+        <v>0.616029795380108</v>
       </c>
       <c r="G5">
-        <v>0.7211157393034704</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>rad_M</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>inversion</t>
-        </is>
+        <v>0.7211167245689978</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>0.6764625204957516</v>
+        <v>0.6764631714934876</v>
       </c>
       <c r="D6">
-        <v>0.02666538509922744</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.02666550481380383</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>0.6221692385846437</v>
+        <v>0.6221696268622112</v>
       </c>
       <c r="G6">
-        <v>0.7263850443729146</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>mix_E</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>notill</t>
-        </is>
+        <v>0.7263858984484993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
       </c>
       <c r="C7">
-        <v>0.8092915233297124</v>
+        <v>0.8092923040852057</v>
       </c>
       <c r="D7">
-        <v>0.01942103115229476</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.01942107493807685</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>0.7683083101535764</v>
+        <v>0.7683089742952789</v>
       </c>
       <c r="G7">
-        <v>0.844492638464187</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>mix_M</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>notill</t>
-        </is>
+        <v>0.8444934771720759</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
       </c>
       <c r="C8">
-        <v>0.7576495775964075</v>
+        <v>0.7576497605592197</v>
       </c>
       <c r="D8">
-        <v>0.02272140849485641</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.02272151595304718</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>0.7103949711296884</v>
+        <v>0.7103949145270413</v>
       </c>
       <c r="G8">
-        <v>0.7993712766725154</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>nocc</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>notill</t>
-        </is>
+        <v>0.7993716404075293</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
       </c>
       <c r="C9">
-        <v>0.7390158890929283</v>
+        <v>0.7390162862122981</v>
       </c>
       <c r="D9">
-        <v>0.02389219032828861</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.02389229326497996</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
       </c>
       <c r="F9">
-        <v>0.6895608129902366</v>
+        <v>0.6895609786709871</v>
       </c>
       <c r="G9">
-        <v>0.7830709430976088</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>rad_L</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>notill</t>
-        </is>
+        <v>0.7830715111459188</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
       </c>
       <c r="C10">
-        <v>0.753859977484449</v>
+        <v>0.7538604362871556</v>
       </c>
       <c r="D10">
-        <v>0.02296771591774253</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.02296780984250087</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
       </c>
       <c r="F10">
-        <v>0.7061389212406833</v>
+        <v>0.7061391652555404</v>
       </c>
       <c r="G10">
-        <v>0.796069507551908</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>rad_M</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>notill</t>
-        </is>
+        <v>0.7960701194630602</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
       </c>
       <c r="C11">
-        <v>0.7657493613969698</v>
+        <v>0.7657500116703474</v>
       </c>
       <c r="D11">
-        <v>0.02226019155075059</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.02226026889398231</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
       </c>
       <c r="F11">
-        <v>0.7193495606389761</v>
+        <v>0.7193500272857293</v>
       </c>
       <c r="G11">
-        <v>0.8065409829366214</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>mix_E</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>surface</t>
-        </is>
+        <v>0.8065417535664107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
       </c>
       <c r="C12">
-        <v>0.7967783992180372</v>
+        <v>0.7967791937906664</v>
       </c>
       <c r="D12">
-        <v>0.02028991438460235</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.02028996546294248</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
       </c>
       <c r="F12">
-        <v>0.7541155344381602</v>
+        <v>0.754116197057247</v>
       </c>
       <c r="G12">
-        <v>0.833671592054723</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>mix_M</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>surface</t>
-        </is>
+        <v>0.8336724574129593</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
       </c>
       <c r="C13">
-        <v>0.7184108934057355</v>
+        <v>0.7184116708481789</v>
       </c>
       <c r="D13">
-        <v>0.02480099252161285</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.02480108833166902</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
       </c>
       <c r="F13">
-        <v>0.6673684301584301</v>
+        <v>0.6673689876675175</v>
       </c>
       <c r="G13">
-        <v>0.7643861215997901</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>nocc</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>surface</t>
-        </is>
+        <v>0.7643870535666276</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>0.7002944379897813</v>
+        <v>0.7002956682628898</v>
       </c>
       <c r="D14">
-        <v>0.02577133549484546</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.02577142090528181</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
       </c>
       <c r="F14">
-        <v>0.6474929362774133</v>
+        <v>0.6474939631607185</v>
       </c>
       <c r="G14">
-        <v>0.7482618372360337</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>rad_L</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>surface</t>
-        </is>
+        <v>0.7482631980755433</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
       </c>
       <c r="C15">
-        <v>0.6905558282982245</v>
+        <v>0.6905564560874164</v>
       </c>
       <c r="D15">
-        <v>0.02606724435558618</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.02606735937086483</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
       </c>
       <c r="F15">
-        <v>0.6372917448766676</v>
+        <v>0.6372921182418837</v>
       </c>
       <c r="G15">
-        <v>0.739199001934479</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>rad_M</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>surface</t>
-        </is>
+        <v>0.7391998232893973</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
       </c>
       <c r="C16">
-        <v>0.7009088999614806</v>
+        <v>0.7009096273623132</v>
       </c>
       <c r="D16">
-        <v>0.02561791320100465</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.02561801891124145</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
       </c>
       <c r="F16">
-        <v>0.6484237923183016</v>
+        <v>0.6484242819008208</v>
       </c>
       <c r="G16">
-        <v>0.7485966004327717</v>
+        <v>0.7485975023039785</v>
       </c>
     </row>
   </sheetData>
